--- a/data/dividends_info_20260718.xlsx
+++ b/data/dividends_info_20260718.xlsx
@@ -4041,7 +4041,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4238,14 +4238,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4255,14 +4255,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4279,7 +4279,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4289,14 +4289,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4415,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4425,14 +4425,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4442,14 +4442,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4466,7 +4466,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4493,14 +4493,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4517,7 +4517,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4534,7 +4534,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4551,7 +4551,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4561,14 +4561,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4765,14 +4765,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4789,7 +4789,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4823,7 +4823,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4840,7 +4840,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4857,7 +4857,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4867,14 +4867,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4891,7 +4891,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4901,14 +4901,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4925,7 +4925,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4935,14 +4935,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4952,14 +4952,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4976,7 +4976,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4993,7 +4993,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5003,14 +5003,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5027,7 +5027,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5037,14 +5037,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5071,14 +5071,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5095,7 +5095,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5112,7 +5112,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5129,7 +5129,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5139,14 +5139,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5173,14 +5173,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5197,7 +5197,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5207,14 +5207,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5224,14 +5224,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5258,14 +5258,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5275,14 +5275,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5292,14 +5292,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5309,14 +5309,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5326,14 +5326,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5343,14 +5343,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5360,14 +5360,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5377,14 +5377,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5394,14 +5394,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5411,14 +5411,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5445,14 +5445,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5462,14 +5462,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5479,14 +5479,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5503,7 +5503,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5537,7 +5537,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5547,14 +5547,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5571,7 +5571,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5588,7 +5588,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5632,14 +5632,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5656,7 +5656,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5666,14 +5666,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5690,7 +5690,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5700,14 +5700,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5717,14 +5717,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5734,14 +5734,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5751,14 +5751,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5775,7 +5775,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5785,14 +5785,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5809,7 +5809,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5819,14 +5819,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5860,7 +5860,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5870,14 +5870,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5887,14 +5887,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5904,14 +5904,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5928,7 +5928,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5945,7 +5945,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5955,14 +5955,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5972,14 +5972,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6013,7 +6013,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6030,7 +6030,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6047,7 +6047,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6098,7 +6098,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6115,7 +6115,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6125,14 +6125,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6149,7 +6149,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6176,14 +6176,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6193,14 +6193,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6210,14 +6210,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6227,14 +6227,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6244,14 +6244,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6268,7 +6268,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6285,7 +6285,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6312,14 +6312,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6329,14 +6329,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6346,14 +6346,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6370,7 +6370,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6380,14 +6380,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6397,14 +6397,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6414,14 +6414,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6438,7 +6438,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6448,14 +6448,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6472,7 +6472,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6506,7 +6506,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6523,7 +6523,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6540,7 +6540,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6608,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
